--- a/Data/t14.1.xlsx
+++ b/Data/t14.1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2723</v>
+        <v>2964</v>
       </c>
       <c r="E2" t="n">
-        <v>-13.36459549823704</v>
+        <v>-13.35240030482089</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5017</v>
+        <v>5472</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.962431974489226</v>
+        <v>-7.953033036331347</v>
       </c>
     </row>
     <row r="4">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4061</v>
+        <v>4426</v>
       </c>
       <c r="E4" t="n">
-        <v>-11.02851832065899</v>
+        <v>-11.06746339521568</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4014</v>
+        <v>4376</v>
       </c>
       <c r="E5" t="n">
-        <v>-15.09253435870747</v>
+        <v>-15.1092306898514</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5044</v>
+        <v>5498</v>
       </c>
       <c r="E6" t="n">
-        <v>-15.29598948120566</v>
+        <v>-15.30370440148451</v>
       </c>
     </row>
     <row r="7">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3491</v>
+        <v>3808</v>
       </c>
       <c r="E7" t="n">
-        <v>-13.89259694768673</v>
+        <v>-13.85590018105298</v>
       </c>
     </row>
     <row r="8">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7002</v>
+        <v>7639</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.60236808028529</v>
+        <v>-12.62169723659447</v>
       </c>
     </row>
     <row r="9">
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7026</v>
+        <v>7660</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.765522102078583</v>
+        <v>-9.760211660267471</v>
       </c>
     </row>
     <row r="10">
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2620</v>
+        <v>2852</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.786405571220341</v>
+        <v>-3.771775501003927</v>
       </c>
     </row>
     <row r="11">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4498</v>
+        <v>4903</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.36090516639435</v>
+        <v>-10.3921351137534</v>
       </c>
     </row>
     <row r="12">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3817</v>
+        <v>4161</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.02581706399673</v>
+        <v>-5.986046479937313</v>
       </c>
     </row>
     <row r="13">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3845</v>
+        <v>4190</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.212107752188354</v>
+        <v>-4.251101160089787</v>
       </c>
     </row>
     <row r="14">
@@ -748,10 +748,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4753</v>
+        <v>5182</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.768616672762161</v>
+        <v>-5.74682623911108</v>
       </c>
     </row>
     <row r="15">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3180</v>
+        <v>3468</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.897376888560816</v>
+        <v>-8.928633795492868</v>
       </c>
     </row>
     <row r="16">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6792</v>
+        <v>7412</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.007052266267096</v>
+        <v>-2.973329325771512</v>
       </c>
     </row>
     <row r="17">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6700</v>
+        <v>7303</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.646301647931594</v>
+        <v>-4.661268091668602</v>
       </c>
     </row>
     <row r="18">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2617</v>
+        <v>2849</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1065950652653358</v>
+        <v>-0.1178605178805747</v>
       </c>
     </row>
     <row r="19">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4607</v>
+        <v>5023</v>
       </c>
       <c r="E19" t="n">
-        <v>2.435344277645446</v>
+        <v>2.449861916678775</v>
       </c>
     </row>
     <row r="20">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3622</v>
+        <v>3948</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.095634313109287</v>
+        <v>-5.106885000004835</v>
       </c>
     </row>
     <row r="21">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3730</v>
+        <v>4067</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.975723492521432</v>
+        <v>-2.934909046362155</v>
       </c>
     </row>
     <row r="22">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4528</v>
+        <v>4935</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.746830341629471</v>
+        <v>-4.780786017713668</v>
       </c>
     </row>
     <row r="23">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2922</v>
+        <v>3185</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.130865365283334</v>
+        <v>-8.160625968452951</v>
       </c>
     </row>
     <row r="24">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6589</v>
+        <v>7187</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.990623555528649</v>
+        <v>-3.025573920309232</v>
       </c>
     </row>
     <row r="25">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6576</v>
+        <v>7168</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.849844891537022</v>
+        <v>-1.852695701595031</v>
       </c>
     </row>
     <row r="26">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2548</v>
+        <v>2774</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.652839432489129</v>
+        <v>-2.642380339924766</v>
       </c>
     </row>
     <row r="27">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4414</v>
+        <v>4813</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.184460105666021</v>
+        <v>-4.188228071860323</v>
       </c>
     </row>
     <row r="28">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3380</v>
+        <v>3684</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.68498239196439</v>
+        <v>-6.698350348071836</v>
       </c>
     </row>
     <row r="29">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3547</v>
+        <v>3867</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.916445271977099</v>
+        <v>-4.930758617563136</v>
       </c>
     </row>
     <row r="30">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4314</v>
+        <v>4704</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.717219252948146</v>
+        <v>-4.669256152329016</v>
       </c>
     </row>
     <row r="31">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2903</v>
+        <v>3166</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.656245643064457</v>
+        <v>-0.6024485932366708</v>
       </c>
     </row>
     <row r="32">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6443</v>
+        <v>7029</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.215850791538809</v>
+        <v>-2.196718436153178</v>
       </c>
     </row>
     <row r="33">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6617</v>
+        <v>7212</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6237633709847312</v>
+        <v>0.6218820358922628</v>
       </c>
     </row>
     <row r="34">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2485</v>
+        <v>2707</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.451933752445501</v>
+        <v>-2.422655203203927</v>
       </c>
     </row>
     <row r="35">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4311</v>
+        <v>4699</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.344578708788825</v>
+        <v>-2.364755900836146</v>
       </c>
     </row>
     <row r="36">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3220</v>
+        <v>3509</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.720665044741034</v>
+        <v>-4.732769057545849</v>
       </c>
     </row>
     <row r="37">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3431</v>
+        <v>3740</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.262974239371708</v>
+        <v>-3.264669114394259</v>
       </c>
     </row>
     <row r="38">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4100</v>
+        <v>4470</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.963657777438335</v>
+        <v>-4.986222860815682</v>
       </c>
     </row>
     <row r="39">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2768</v>
+        <v>3018</v>
       </c>
       <c r="E39" t="n">
-        <v>-4.634174955040926</v>
+        <v>-4.655869159430647</v>
       </c>
     </row>
     <row r="40">
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6122</v>
+        <v>6678</v>
       </c>
       <c r="E40" t="n">
-        <v>-4.977715482385204</v>
+        <v>-4.999397742466205</v>
       </c>
     </row>
     <row r="41">
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6351</v>
+        <v>6923</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.007352865501557</v>
+        <v>-4.012613743956006</v>
       </c>
     </row>
     <row r="42">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2464</v>
+        <v>2683</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.8280624132782521</v>
+        <v>-0.8787863687283792</v>
       </c>
     </row>
     <row r="43">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4325</v>
+        <v>4716</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3283893794886028</v>
+        <v>0.3526076981742898</v>
       </c>
     </row>
     <row r="44">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3008</v>
+        <v>3278</v>
       </c>
       <c r="E44" t="n">
-        <v>-6.58230865520374</v>
+        <v>-6.598439463230566</v>
       </c>
     </row>
     <row r="45">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3284</v>
+        <v>3581</v>
       </c>
       <c r="E45" t="n">
-        <v>-4.284988984988813</v>
+        <v>-4.251014382552231</v>
       </c>
     </row>
     <row r="46">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3633</v>
+        <v>3961</v>
       </c>
       <c r="E46" t="n">
-        <v>-11.39214458311004</v>
+        <v>-11.38186630692451</v>
       </c>
     </row>
     <row r="47">
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2500</v>
+        <v>2727</v>
       </c>
       <c r="E47" t="n">
-        <v>-9.673516829155504</v>
+        <v>-9.659692113148132</v>
       </c>
     </row>
     <row r="48">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5912</v>
+        <v>6448</v>
       </c>
       <c r="E48" t="n">
-        <v>-3.425289057340097</v>
+        <v>-3.44497399286523</v>
       </c>
     </row>
     <row r="49">
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6224</v>
+        <v>6781</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.010174089422767</v>
+        <v>-2.052860501833353</v>
       </c>
     </row>
     <row r="50">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2107</v>
+        <v>2294</v>
       </c>
       <c r="E50" t="n">
-        <v>-14.50806461253442</v>
+        <v>-14.50713008038689</v>
       </c>
     </row>
     <row r="51">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3302</v>
+        <v>3599</v>
       </c>
       <c r="E51" t="n">
-        <v>-23.65399563868147</v>
+        <v>-23.68585781027598</v>
       </c>
     </row>
     <row r="52">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2635</v>
+        <v>2872</v>
       </c>
       <c r="E52" t="n">
-        <v>-12.41928996513653</v>
+        <v>-12.38887043479443</v>
       </c>
     </row>
     <row r="53">
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2768</v>
+        <v>3018</v>
       </c>
       <c r="E53" t="n">
-        <v>-15.71193404818513</v>
+        <v>-15.72769290158681</v>
       </c>
     </row>
     <row r="54">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3302</v>
+        <v>3600</v>
       </c>
       <c r="E54" t="n">
-        <v>-9.109343841200046</v>
+        <v>-9.110739376174736</v>
       </c>
     </row>
     <row r="55">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2177</v>
+        <v>2373</v>
       </c>
       <c r="E55" t="n">
-        <v>-12.9463950508338</v>
+        <v>-12.95663652346427</v>
       </c>
     </row>
     <row r="56">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4862</v>
+        <v>5303</v>
       </c>
       <c r="E56" t="n">
-        <v>-17.75617818418527</v>
+        <v>-17.75250300565592</v>
       </c>
     </row>
     <row r="57">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4937</v>
+        <v>5381</v>
       </c>
       <c r="E57" t="n">
-        <v>-20.68037482983345</v>
+        <v>-20.64802944909133</v>
       </c>
     </row>
     <row r="58">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2269</v>
+        <v>2470</v>
       </c>
       <c r="E58" t="n">
-        <v>7.701108851771821</v>
+        <v>7.693860733391578</v>
       </c>
     </row>
     <row r="59">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3309</v>
+        <v>3607</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2111261371857243</v>
+        <v>0.2190420298645801</v>
       </c>
     </row>
     <row r="60">
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2819</v>
+        <v>3072</v>
       </c>
       <c r="E60" t="n">
-        <v>6.977271611627245</v>
+        <v>6.95493346654168</v>
       </c>
     </row>
     <row r="61">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2804</v>
+        <v>3058</v>
       </c>
       <c r="E61" t="n">
-        <v>1.306151391111587</v>
+        <v>1.313281249102816</v>
       </c>
     </row>
     <row r="62">
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3385</v>
+        <v>3689</v>
       </c>
       <c r="E62" t="n">
-        <v>2.502994782683166</v>
+        <v>2.472413318950784</v>
       </c>
     </row>
     <row r="63">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2257</v>
+        <v>2461</v>
       </c>
       <c r="E63" t="n">
-        <v>3.702222611681294</v>
+        <v>3.685682838160798</v>
       </c>
     </row>
     <row r="64">
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5029</v>
+        <v>5484</v>
       </c>
       <c r="E64" t="n">
-        <v>3.418255429744788</v>
+        <v>3.415147835843313</v>
       </c>
     </row>
     <row r="65">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4858</v>
+        <v>5295</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.603048372197136</v>
+        <v>-1.600760790236211</v>
       </c>
     </row>
     <row r="66">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2194</v>
+        <v>2389</v>
       </c>
       <c r="E66" t="n">
-        <v>-3.30832533822718</v>
+        <v>-3.26653357815192</v>
       </c>
     </row>
     <row r="67">
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3343</v>
+        <v>3643</v>
       </c>
       <c r="E67" t="n">
-        <v>1.032140339483845</v>
+        <v>1.007580687484744</v>
       </c>
     </row>
     <row r="68">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2616</v>
+        <v>2852</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.206454010376628</v>
+        <v>-7.157160333861579</v>
       </c>
     </row>
     <row r="69">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2831</v>
+        <v>3087</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9657790410997569</v>
+        <v>0.9447260801287882</v>
       </c>
     </row>
     <row r="70">
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3197</v>
+        <v>3486</v>
       </c>
       <c r="E70" t="n">
-        <v>-5.532099813410019</v>
+        <v>-5.513339304332698</v>
       </c>
     </row>
     <row r="71">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2236</v>
+        <v>2439</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9337258888277633</v>
+        <v>-0.908215904984</v>
       </c>
     </row>
     <row r="72">
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4860</v>
+        <v>5300</v>
       </c>
       <c r="E72" t="n">
-        <v>-3.353878132335597</v>
+        <v>-3.3607937664765</v>
       </c>
     </row>
     <row r="73">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4791</v>
+        <v>5222</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.374126144044485</v>
+        <v>-1.361718145774038</v>
       </c>
     </row>
     <row r="74">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2082</v>
+        <v>2268</v>
       </c>
       <c r="E74" t="n">
-        <v>-5.109889336070572</v>
+        <v>-5.088560571324252</v>
       </c>
     </row>
     <row r="75">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3299</v>
+        <v>3595</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.318156833080675</v>
+        <v>-1.317214490268115</v>
       </c>
     </row>
     <row r="76">
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2635</v>
+        <v>2871</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7440778324482311</v>
+        <v>0.693007626447506</v>
       </c>
     </row>
     <row r="77">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2804</v>
+        <v>3056</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9708887587138282</v>
+        <v>-0.9942125429861171</v>
       </c>
     </row>
     <row r="78">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3270</v>
+        <v>3565</v>
       </c>
       <c r="E78" t="n">
-        <v>2.272146154565458</v>
+        <v>2.27136156038108</v>
       </c>
     </row>
     <row r="79">
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2255</v>
+        <v>2459</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8475024358109984</v>
+        <v>0.8216235679642026</v>
       </c>
     </row>
     <row r="80">
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4868</v>
+        <v>5310</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1651391196733965</v>
+        <v>0.1915160863499965</v>
       </c>
     </row>
     <row r="81">
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4641</v>
+        <v>5059</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.126537087026704</v>
+        <v>-3.131159117223559</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2308,20 +2308,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1283</v>
+        <v>2376</v>
       </c>
       <c r="E82" t="n">
-        <v>-17.65513301948977</v>
+        <v>4.773474197701755</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2331,20 +2331,20 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3025</v>
+        <v>3529</v>
       </c>
       <c r="E83" t="n">
-        <v>-16.29144918310254</v>
+        <v>-1.836830796481748</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2354,20 +2354,20 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2775</v>
+        <v>2907</v>
       </c>
       <c r="E84" t="n">
-        <v>-16.79833340335555</v>
+        <v>1.238398363730497</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2377,20 +2377,20 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2854</v>
+        <v>2955</v>
       </c>
       <c r="E85" t="n">
-        <v>-16.53023488955935</v>
+        <v>-3.304595001403798</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2400,20 +2400,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3595</v>
+        <v>3534</v>
       </c>
       <c r="E86" t="n">
-        <v>-12.67609477675105</v>
+        <v>-0.8639491893039808</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2423,20 +2423,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2470</v>
+        <v>2413</v>
       </c>
       <c r="E87" t="n">
-        <v>-20.74813602799415</v>
+        <v>-1.852850441268916</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4916</v>
+        <v>5389</v>
       </c>
       <c r="E88" t="n">
-        <v>-12.86475529482465</v>
+        <v>1.484257216598461</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2469,14 +2469,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5395</v>
+        <v>5078</v>
       </c>
       <c r="E89" t="n">
-        <v>-10.1699930923048</v>
+        <v>0.3774305119800925</v>
       </c>
     </row>
     <row r="90">
@@ -2492,14 +2492,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1204</v>
+        <v>1402</v>
       </c>
       <c r="E90" t="n">
-        <v>-6.147725384388991</v>
+        <v>-17.58502647298948</v>
       </c>
     </row>
     <row r="91">
@@ -2515,14 +2515,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2739</v>
+        <v>3309</v>
       </c>
       <c r="E91" t="n">
-        <v>-9.455201728867301</v>
+        <v>-16.31210624584966</v>
       </c>
     </row>
     <row r="92">
@@ -2538,14 +2538,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2599</v>
+        <v>3033</v>
       </c>
       <c r="E92" t="n">
-        <v>-6.344620113889954</v>
+        <v>-16.82707019765558</v>
       </c>
     </row>
     <row r="93">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2770</v>
+        <v>3119</v>
       </c>
       <c r="E93" t="n">
-        <v>-2.946562529282892</v>
+        <v>-16.56371478075913</v>
       </c>
     </row>
     <row r="94">
@@ -2584,14 +2584,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3002</v>
+        <v>3931</v>
       </c>
       <c r="E94" t="n">
-        <v>-16.50302706904252</v>
+        <v>-12.68124064487917</v>
       </c>
     </row>
     <row r="95">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2376</v>
+        <v>2701</v>
       </c>
       <c r="E95" t="n">
-        <v>-3.809183758184198</v>
+        <v>-20.80540281465113</v>
       </c>
     </row>
     <row r="96">
@@ -2630,14 +2630,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4716</v>
+        <v>5376</v>
       </c>
       <c r="E96" t="n">
-        <v>-4.071206890109935</v>
+        <v>-12.92603375786426</v>
       </c>
     </row>
     <row r="97">
@@ -2653,14 +2653,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5290</v>
+        <v>5900</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.947597336000884</v>
+        <v>-10.17053365482108</v>
       </c>
     </row>
     <row r="98">
@@ -2676,14 +2676,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1243</v>
+        <v>1315</v>
       </c>
       <c r="E98" t="n">
-        <v>3.252995493143884</v>
+        <v>-6.247662378728047</v>
       </c>
     </row>
     <row r="99">
@@ -2699,14 +2699,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3102</v>
+        <v>2997</v>
       </c>
       <c r="E99" t="n">
-        <v>13.27372395972359</v>
+        <v>-9.430085320714321</v>
       </c>
     </row>
     <row r="100">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2741</v>
+        <v>2842</v>
       </c>
       <c r="E100" t="n">
-        <v>5.472516266308358</v>
+        <v>-6.324830085114142</v>
       </c>
     </row>
     <row r="101">
@@ -2745,14 +2745,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2738</v>
+        <v>3029</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.142413040952983</v>
+        <v>-2.884229869428001</v>
       </c>
     </row>
     <row r="102">
@@ -2768,14 +2768,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3082</v>
+        <v>3282</v>
       </c>
       <c r="E102" t="n">
-        <v>2.669778123919686</v>
+        <v>-16.52311556438597</v>
       </c>
     </row>
     <row r="103">
@@ -2791,14 +2791,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2132</v>
+        <v>2598</v>
       </c>
       <c r="E103" t="n">
-        <v>-10.27899908873964</v>
+        <v>-3.792069274640208</v>
       </c>
     </row>
     <row r="104">
@@ -2814,14 +2814,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4593</v>
+        <v>5159</v>
       </c>
       <c r="E104" t="n">
-        <v>-2.618049559941582</v>
+        <v>-4.041807934207409</v>
       </c>
     </row>
     <row r="105">
@@ -2837,14 +2837,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5100</v>
+        <v>5785</v>
       </c>
       <c r="E105" t="n">
-        <v>-3.600162647360339</v>
+        <v>-1.948751690591377</v>
       </c>
     </row>
     <row r="106">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1175</v>
+        <v>1358</v>
       </c>
       <c r="E106" t="n">
-        <v>-5.513516259280237</v>
+        <v>3.322572983368355</v>
       </c>
     </row>
     <row r="107">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2731</v>
+        <v>3393</v>
       </c>
       <c r="E107" t="n">
-        <v>-11.95694207634427</v>
+        <v>13.21757930467589</v>
       </c>
     </row>
     <row r="108">
@@ -2906,14 +2906,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2347</v>
+        <v>2997</v>
       </c>
       <c r="E108" t="n">
-        <v>-14.37674093440784</v>
+        <v>5.456933528870067</v>
       </c>
     </row>
     <row r="109">
@@ -2929,14 +2929,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2580</v>
+        <v>2995</v>
       </c>
       <c r="E109" t="n">
-        <v>-5.796404619660911</v>
+        <v>-1.123120678598954</v>
       </c>
     </row>
     <row r="110">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2969</v>
+        <v>3370</v>
       </c>
       <c r="E110" t="n">
-        <v>-3.655521019356833</v>
+        <v>2.688959059952878</v>
       </c>
     </row>
     <row r="111">
@@ -2975,14 +2975,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2142</v>
+        <v>2331</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5038397846341081</v>
+        <v>-10.28161044565536</v>
       </c>
     </row>
     <row r="112">
@@ -2998,14 +2998,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4748</v>
+        <v>5022</v>
       </c>
       <c r="E112" t="n">
-        <v>3.391537001882083</v>
+        <v>-2.658721070296355</v>
       </c>
     </row>
     <row r="113">
@@ -3021,14 +3021,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5148</v>
+        <v>5576</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9484328808110787</v>
+        <v>-3.617851238558134</v>
       </c>
     </row>
     <row r="114">
@@ -3044,14 +3044,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1176</v>
+        <v>1283</v>
       </c>
       <c r="E114" t="n">
-        <v>0.07452545948578582</v>
+        <v>-5.533870952029196</v>
       </c>
     </row>
     <row r="115">
@@ -3067,14 +3067,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2516</v>
+        <v>2989</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.890923265937988</v>
+        <v>-11.91021561085258</v>
       </c>
     </row>
     <row r="116">
@@ -3090,14 +3090,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2105</v>
+        <v>2565</v>
       </c>
       <c r="E116" t="n">
-        <v>-10.32648351162602</v>
+        <v>-14.4118054497354</v>
       </c>
     </row>
     <row r="117">
@@ -3113,14 +3113,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2516</v>
+        <v>2820</v>
       </c>
       <c r="E117" t="n">
-        <v>-2.472742281581397</v>
+        <v>-5.839575104439277</v>
       </c>
     </row>
     <row r="118">
@@ -3136,14 +3136,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2759</v>
+        <v>3247</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.094869263609571</v>
+        <v>-3.653422034844334</v>
       </c>
     </row>
     <row r="119">
@@ -3159,14 +3159,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2023</v>
+        <v>2343</v>
       </c>
       <c r="E119" t="n">
-        <v>-5.561156710606396</v>
+        <v>0.4992836470129491</v>
       </c>
     </row>
     <row r="120">
@@ -3182,14 +3182,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4051</v>
+        <v>5195</v>
       </c>
       <c r="E120" t="n">
-        <v>-14.69646012533687</v>
+        <v>3.441843612631734</v>
       </c>
     </row>
     <row r="121">
@@ -3205,14 +3205,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5182</v>
+        <v>5629</v>
       </c>
       <c r="E121" t="n">
-        <v>0.6677962291334882</v>
+        <v>0.944923860231861</v>
       </c>
     </row>
     <row r="122">
@@ -3228,14 +3228,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1236</v>
+        <v>1284</v>
       </c>
       <c r="E122" t="n">
-        <v>5.126114964335549</v>
+        <v>0.1012529818092078</v>
       </c>
     </row>
     <row r="123">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2547</v>
+        <v>2751</v>
       </c>
       <c r="E123" t="n">
-        <v>1.261116486584668</v>
+        <v>-7.946479927610806</v>
       </c>
     </row>
     <row r="124">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2139</v>
+        <v>2302</v>
       </c>
       <c r="E124" t="n">
-        <v>1.623531773895848</v>
+        <v>-10.25938667933995</v>
       </c>
     </row>
     <row r="125">
@@ -3297,14 +3297,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2355</v>
+        <v>2751</v>
       </c>
       <c r="E125" t="n">
-        <v>-6.403258746234508</v>
+        <v>-2.450747385975627</v>
       </c>
     </row>
     <row r="126">
@@ -3320,14 +3320,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2551</v>
+        <v>3015</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.516091936355207</v>
+        <v>-7.12838349658762</v>
       </c>
     </row>
     <row r="127">
@@ -3343,14 +3343,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1807</v>
+        <v>2213</v>
       </c>
       <c r="E127" t="n">
-        <v>-10.69651553793615</v>
+        <v>-5.553977761547624</v>
       </c>
     </row>
     <row r="128">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4079</v>
+        <v>4431</v>
       </c>
       <c r="E128" t="n">
-        <v>0.6902414883362518</v>
+        <v>-14.70934722659382</v>
       </c>
     </row>
     <row r="129">
@@ -3389,14 +3389,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4700</v>
+        <v>5666</v>
       </c>
       <c r="E129" t="n">
-        <v>-9.29951842667216</v>
+        <v>0.6676758952670614</v>
       </c>
     </row>
     <row r="130">
@@ -3412,14 +3412,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>976</v>
+        <v>1350</v>
       </c>
       <c r="E130" t="n">
-        <v>-21.06179399059724</v>
+        <v>5.110818998358924</v>
       </c>
     </row>
     <row r="131">
@@ -3435,14 +3435,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2152</v>
+        <v>2788</v>
       </c>
       <c r="E131" t="n">
-        <v>-15.51733064008177</v>
+        <v>1.340063964839322</v>
       </c>
     </row>
     <row r="132">
@@ -3458,14 +3458,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1760</v>
+        <v>2339</v>
       </c>
       <c r="E132" t="n">
-        <v>-17.71183399737801</v>
+        <v>1.635966713083126</v>
       </c>
     </row>
     <row r="133">
@@ -3481,14 +3481,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2037</v>
+        <v>2575</v>
       </c>
       <c r="E133" t="n">
-        <v>-13.47727109265201</v>
+        <v>-6.403207398281163</v>
       </c>
     </row>
     <row r="134">
@@ -3504,14 +3504,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2259</v>
+        <v>2789</v>
       </c>
       <c r="E134" t="n">
-        <v>-11.46049669580558</v>
+        <v>-7.501160934347995</v>
       </c>
     </row>
     <row r="135">
@@ -3527,14 +3527,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1621</v>
+        <v>1977</v>
       </c>
       <c r="E135" t="n">
-        <v>-10.29708009252714</v>
+        <v>-10.6405482898567</v>
       </c>
     </row>
     <row r="136">
@@ -3550,14 +3550,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3453</v>
+        <v>4461</v>
       </c>
       <c r="E136" t="n">
-        <v>-15.34265799753285</v>
+        <v>0.6960731820502941</v>
       </c>
     </row>
     <row r="137">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3802</v>
+        <v>5139</v>
       </c>
       <c r="E137" t="n">
-        <v>-19.11327763133602</v>
+        <v>-9.303463759098275</v>
       </c>
     </row>
     <row r="138">
@@ -3596,14 +3596,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1020</v>
+        <v>1066</v>
       </c>
       <c r="E138" t="n">
-        <v>4.535182297295282</v>
+        <v>-21.05864673352289</v>
       </c>
     </row>
     <row r="139">
@@ -3619,14 +3619,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2054</v>
+        <v>2354</v>
       </c>
       <c r="E139" t="n">
-        <v>-4.551437609237807</v>
+        <v>-15.56300435439217</v>
       </c>
     </row>
     <row r="140">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1786</v>
+        <v>1923</v>
       </c>
       <c r="E140" t="n">
-        <v>1.44820051741712</v>
+        <v>-17.77725406632889</v>
       </c>
     </row>
     <row r="141">
@@ -3665,14 +3665,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1943</v>
+        <v>2227</v>
       </c>
       <c r="E141" t="n">
-        <v>-4.607389418210439</v>
+        <v>-13.51039126434861</v>
       </c>
     </row>
     <row r="142">
@@ -3688,14 +3688,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2267</v>
+        <v>2470</v>
       </c>
       <c r="E142" t="n">
-        <v>0.3575506519300831</v>
+        <v>-11.43985394264584</v>
       </c>
     </row>
     <row r="143">
@@ -3711,14 +3711,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1545</v>
+        <v>1772</v>
       </c>
       <c r="E143" t="n">
-        <v>-4.656714132708584</v>
+        <v>-10.36496658535073</v>
       </c>
     </row>
     <row r="144">
@@ -3734,14 +3734,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3198</v>
+        <v>3778</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.37459478051441</v>
+        <v>-15.32325211044633</v>
       </c>
     </row>
     <row r="145">
@@ -3757,14 +3757,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3795</v>
+        <v>4158</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.1897403015452714</v>
+        <v>-19.09807766334823</v>
       </c>
     </row>
     <row r="146">
@@ -3780,14 +3780,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1047</v>
+        <v>1115</v>
       </c>
       <c r="E146" t="n">
-        <v>2.674567966099373</v>
+        <v>4.617475381378311</v>
       </c>
     </row>
     <row r="147">
@@ -3803,14 +3803,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2099</v>
+        <v>2247</v>
       </c>
       <c r="E147" t="n">
-        <v>2.166058804860294</v>
+        <v>-4.545754990590146</v>
       </c>
     </row>
     <row r="148">
@@ -3826,14 +3826,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1798</v>
+        <v>1952</v>
       </c>
       <c r="E148" t="n">
-        <v>0.6908641919131542</v>
+        <v>1.487352910412687</v>
       </c>
     </row>
     <row r="149">
@@ -3849,14 +3849,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2009</v>
+        <v>2125</v>
       </c>
       <c r="E149" t="n">
-        <v>3.350392812357006</v>
+        <v>-4.595809848701304</v>
       </c>
     </row>
     <row r="150">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2158</v>
+        <v>2479</v>
       </c>
       <c r="E150" t="n">
-        <v>-4.787007635964602</v>
+        <v>0.3642557162337967</v>
       </c>
     </row>
     <row r="151">
@@ -3895,14 +3895,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1501</v>
+        <v>1690</v>
       </c>
       <c r="E151" t="n">
-        <v>-2.856808096575991</v>
+        <v>-4.629878142189858</v>
       </c>
     </row>
     <row r="152">
@@ -3918,14 +3918,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3265</v>
+        <v>3498</v>
       </c>
       <c r="E152" t="n">
-        <v>2.105908950580071</v>
+        <v>-7.405962647411179</v>
       </c>
     </row>
     <row r="153">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3580</v>
+        <v>4149</v>
       </c>
       <c r="E153" t="n">
-        <v>-5.660199467695081</v>
+        <v>-0.21545659160499</v>
       </c>
     </row>
     <row r="154">
@@ -3964,14 +3964,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1094</v>
+        <v>1144</v>
       </c>
       <c r="E154" t="n">
-        <v>4.462710439472661</v>
+        <v>2.641362977614148</v>
       </c>
     </row>
     <row r="155">
@@ -3987,14 +3987,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2111</v>
+        <v>2296</v>
       </c>
       <c r="E155" t="n">
-        <v>0.5850917619807161</v>
+        <v>2.198340114160224</v>
       </c>
     </row>
     <row r="156">
@@ -4010,14 +4010,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1690</v>
+        <v>1966</v>
       </c>
       <c r="E156" t="n">
-        <v>-5.999094631162794</v>
+        <v>0.7344423668201649</v>
       </c>
     </row>
     <row r="157">
@@ -4033,14 +4033,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2056</v>
+        <v>2196</v>
       </c>
       <c r="E157" t="n">
-        <v>2.361599105241075</v>
+        <v>3.3509734442845</v>
       </c>
     </row>
     <row r="158">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2193</v>
+        <v>2360</v>
       </c>
       <c r="E158" t="n">
-        <v>1.599539929382021</v>
+        <v>-4.813861471207403</v>
       </c>
     </row>
     <row r="159">
@@ -4079,14 +4079,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1609</v>
+        <v>1642</v>
       </c>
       <c r="E159" t="n">
-        <v>7.182154435579546</v>
+        <v>-2.864977962315773</v>
       </c>
     </row>
     <row r="160">
@@ -4102,14 +4102,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3282</v>
+        <v>3571</v>
       </c>
       <c r="E160" t="n">
-        <v>0.5055355335793044</v>
+        <v>2.082195499546424</v>
       </c>
     </row>
     <row r="161">
@@ -4125,20 +4125,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3705</v>
+        <v>3914</v>
       </c>
       <c r="E161" t="n">
-        <v>3.492043071637374</v>
+        <v>-5.655326237334435</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4148,20 +4148,20 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1406</v>
+        <v>1196</v>
       </c>
       <c r="E162" t="n">
-        <v>-16.23222487315936</v>
+        <v>4.502382663098592</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4171,20 +4171,20 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>3497</v>
+        <v>2308</v>
       </c>
       <c r="E163" t="n">
-        <v>-14.62067238148974</v>
+        <v>0.5219767691712507</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4194,20 +4194,20 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2748</v>
+        <v>1847</v>
       </c>
       <c r="E164" t="n">
-        <v>-17.08204648083198</v>
+        <v>-6.093240542878386</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4217,20 +4217,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3246</v>
+        <v>2248</v>
       </c>
       <c r="E165" t="n">
-        <v>-11.02984600056589</v>
+        <v>2.371313596946978</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4240,20 +4240,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3674</v>
+        <v>2398</v>
       </c>
       <c r="E166" t="n">
-        <v>-20.48513039869849</v>
+        <v>1.621277445282954</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4263,20 +4263,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2250</v>
+        <v>1760</v>
       </c>
       <c r="E167" t="n">
-        <v>-25.92555981875233</v>
+        <v>7.204240882119395</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4286,20 +4286,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4815</v>
+        <v>3590</v>
       </c>
       <c r="E168" t="n">
-        <v>-16.08793072164759</v>
+        <v>0.5303847099495496</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4309,20 +4309,20 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>6133</v>
+        <v>4051</v>
       </c>
       <c r="E169" t="n">
-        <v>-18.80698927483271</v>
+        <v>3.489468954137354</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4332,20 +4332,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1399</v>
+        <v>1248</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.5246605415571759</v>
+        <v>4.355498593256613</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4355,20 +4355,20 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3730</v>
+        <v>2321</v>
       </c>
       <c r="E171" t="n">
-        <v>6.668223066046974</v>
+        <v>0.545281387342067</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2676</v>
+        <v>1924</v>
       </c>
       <c r="E172" t="n">
-        <v>-2.615747252091083</v>
+        <v>4.195911085997017</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>2644</v>
+        <v>2124</v>
       </c>
       <c r="E173" t="n">
-        <v>-18.55824374935762</v>
+        <v>-5.513464353038189</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4424,20 +4424,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3170</v>
+        <v>2431</v>
       </c>
       <c r="E174" t="n">
-        <v>-13.7259757450408</v>
+        <v>1.372765116707519</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4447,20 +4447,20 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2642</v>
+        <v>1648</v>
       </c>
       <c r="E175" t="n">
-        <v>17.40680009142728</v>
+        <v>-6.362688667320382</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4470,20 +4470,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4941</v>
+        <v>3585</v>
       </c>
       <c r="E176" t="n">
-        <v>2.606222733031216</v>
+        <v>-0.1343099437221551</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4493,14 +4493,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>7169</v>
+        <v>4005</v>
       </c>
       <c r="E177" t="n">
-        <v>16.89592620443971</v>
+        <v>-1.127465446842379</v>
       </c>
     </row>
     <row r="178">
@@ -4516,14 +4516,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1607</v>
+        <v>1541</v>
       </c>
       <c r="E178" t="n">
-        <v>14.89207372853651</v>
+        <v>-16.1874053038031</v>
       </c>
     </row>
     <row r="179">
@@ -4539,14 +4539,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2936</v>
+        <v>3828</v>
       </c>
       <c r="E179" t="n">
-        <v>-21.29157089371418</v>
+        <v>-14.64108459414637</v>
       </c>
     </row>
     <row r="180">
@@ -4562,14 +4562,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>3020</v>
+        <v>3009</v>
       </c>
       <c r="E180" t="n">
-        <v>12.84077364607867</v>
+        <v>-17.09019305158006</v>
       </c>
     </row>
     <row r="181">
@@ -4585,14 +4585,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>3018</v>
+        <v>3552</v>
       </c>
       <c r="E181" t="n">
-        <v>14.18237097780677</v>
+        <v>-11.0465393019703</v>
       </c>
     </row>
     <row r="182">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>2260</v>
+        <v>4022</v>
       </c>
       <c r="E182" t="n">
-        <v>-28.6963652495768</v>
+        <v>-20.49040710237385</v>
       </c>
     </row>
     <row r="183">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2250</v>
+        <v>2463</v>
       </c>
       <c r="E183" t="n">
-        <v>-14.83433284350379</v>
+        <v>-25.94155895054597</v>
       </c>
     </row>
     <row r="184">
@@ -4654,14 +4654,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4045</v>
+        <v>5271</v>
       </c>
       <c r="E184" t="n">
-        <v>-18.12198697327576</v>
+        <v>-16.07153031961377</v>
       </c>
     </row>
     <row r="185">
@@ -4677,14 +4677,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>5435</v>
+        <v>6714</v>
       </c>
       <c r="E185" t="n">
-        <v>-24.1961018163057</v>
+        <v>-18.790973494595</v>
       </c>
     </row>
     <row r="186">
@@ -4700,14 +4700,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1395</v>
+        <v>1532</v>
       </c>
       <c r="E186" t="n">
-        <v>-13.22333620146095</v>
+        <v>-0.5828871406593716</v>
       </c>
     </row>
     <row r="187">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2994</v>
+        <v>4085</v>
       </c>
       <c r="E187" t="n">
-        <v>1.984324544968996</v>
+        <v>6.720345558400775</v>
       </c>
     </row>
     <row r="188">
@@ -4746,14 +4746,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2223</v>
+        <v>2930</v>
       </c>
       <c r="E188" t="n">
-        <v>-26.38246433387885</v>
+        <v>-2.618413852659185</v>
       </c>
     </row>
     <row r="189">
@@ -4769,14 +4769,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2509</v>
+        <v>2893</v>
       </c>
       <c r="E189" t="n">
-        <v>-16.89275367561114</v>
+        <v>-18.57107602133761</v>
       </c>
     </row>
     <row r="190">
@@ -4792,14 +4792,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2826</v>
+        <v>3469</v>
       </c>
       <c r="E190" t="n">
-        <v>25.02938303570568</v>
+        <v>-13.74026574877388</v>
       </c>
     </row>
     <row r="191">
@@ -4815,14 +4815,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>2202</v>
+        <v>2893</v>
       </c>
       <c r="E191" t="n">
-        <v>-2.125531216195053</v>
+        <v>17.43194655384357</v>
       </c>
     </row>
     <row r="192">
@@ -4838,14 +4838,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4002</v>
+        <v>5407</v>
       </c>
       <c r="E192" t="n">
-        <v>-1.063821278417754</v>
+        <v>2.583626786809123</v>
       </c>
     </row>
     <row r="193">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>5625</v>
+        <v>7847</v>
       </c>
       <c r="E193" t="n">
-        <v>3.510647249273613</v>
+        <v>16.87196359997849</v>
       </c>
     </row>
     <row r="194">
@@ -4884,14 +4884,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1125</v>
+        <v>1760</v>
       </c>
       <c r="E194" t="n">
-        <v>-19.34153909182717</v>
+        <v>14.93229897269324</v>
       </c>
     </row>
     <row r="195">
@@ -4907,14 +4907,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2506</v>
+        <v>3213</v>
       </c>
       <c r="E195" t="n">
-        <v>-16.29618447502986</v>
+        <v>-21.33196127810479</v>
       </c>
     </row>
     <row r="196">
@@ -4930,14 +4930,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2102</v>
+        <v>3307</v>
       </c>
       <c r="E196" t="n">
-        <v>-5.449088569661709</v>
+        <v>12.86390149474561</v>
       </c>
     </row>
     <row r="197">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2384</v>
+        <v>3304</v>
       </c>
       <c r="E197" t="n">
-        <v>-4.979623797230259</v>
+        <v>14.21141473540559</v>
       </c>
     </row>
     <row r="198">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>2572</v>
+        <v>2474</v>
       </c>
       <c r="E198" t="n">
-        <v>-8.992799655003436</v>
+        <v>-28.68809986094859</v>
       </c>
     </row>
     <row r="199">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1997</v>
+        <v>2464</v>
       </c>
       <c r="E199" t="n">
-        <v>-9.340109120800133</v>
+        <v>-14.8359733331251</v>
       </c>
     </row>
     <row r="200">
@@ -5022,14 +5022,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>3339</v>
+        <v>4429</v>
       </c>
       <c r="E200" t="n">
-        <v>-16.56667837201178</v>
+        <v>-18.09638408716319</v>
       </c>
     </row>
     <row r="201">
@@ -5045,14 +5045,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>5337</v>
+        <v>5949</v>
       </c>
       <c r="E201" t="n">
-        <v>-5.124815967845975</v>
+        <v>-24.18250763547957</v>
       </c>
     </row>
     <row r="202">
@@ -5068,14 +5068,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1119</v>
+        <v>1527</v>
       </c>
       <c r="E202" t="n">
-        <v>-0.5768090394207226</v>
+        <v>-13.25756271735551</v>
       </c>
     </row>
     <row r="203">
@@ -5091,14 +5091,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>2417</v>
+        <v>3279</v>
       </c>
       <c r="E203" t="n">
-        <v>-3.558003564645762</v>
+        <v>2.035714025913227</v>
       </c>
     </row>
     <row r="204">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>2097</v>
+        <v>2434</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.2521001183013682</v>
+        <v>-26.39096590214972</v>
       </c>
     </row>
     <row r="205">
@@ -5137,14 +5137,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2878</v>
+        <v>2746</v>
       </c>
       <c r="E205" t="n">
-        <v>20.7490223647125</v>
+        <v>-16.87820734087506</v>
       </c>
     </row>
     <row r="206">
@@ -5160,14 +5160,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2227</v>
+        <v>3093</v>
       </c>
       <c r="E206" t="n">
-        <v>-13.40836658780894</v>
+        <v>25.0190741629136</v>
       </c>
     </row>
     <row r="207">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>2221</v>
+        <v>2411</v>
       </c>
       <c r="E207" t="n">
-        <v>11.21904318274691</v>
+        <v>-2.137405550932003</v>
       </c>
     </row>
     <row r="208">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>4207</v>
+        <v>4380</v>
       </c>
       <c r="E208" t="n">
-        <v>26.00253412947115</v>
+        <v>-1.086720097424365</v>
       </c>
     </row>
     <row r="209">
@@ -5229,14 +5229,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>5338</v>
+        <v>6159</v>
       </c>
       <c r="E209" t="n">
-        <v>0.008299710610204514</v>
+        <v>3.513357225156111</v>
       </c>
     </row>
     <row r="210">
@@ -5252,14 +5252,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1067</v>
+        <v>1232</v>
       </c>
       <c r="E210" t="n">
-        <v>-4.577600128497661</v>
+        <v>-19.34754184591016</v>
       </c>
     </row>
     <row r="211">
@@ -5275,14 +5275,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2435</v>
+        <v>2743</v>
       </c>
       <c r="E211" t="n">
-        <v>0.7461452843015914</v>
+        <v>-16.35105440743488</v>
       </c>
     </row>
     <row r="212">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>2122</v>
+        <v>2302</v>
       </c>
       <c r="E212" t="n">
-        <v>1.206211118281364</v>
+        <v>-5.44325358520793</v>
       </c>
     </row>
     <row r="213">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1764</v>
+        <v>2609</v>
       </c>
       <c r="E213" t="n">
-        <v>-38.72881356964296</v>
+        <v>-4.989803210101296</v>
       </c>
     </row>
     <row r="214">
@@ -5344,14 +5344,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2228</v>
+        <v>2815</v>
       </c>
       <c r="E214" t="n">
-        <v>0.02794848915363968</v>
+        <v>-8.987192647837084</v>
       </c>
     </row>
     <row r="215">
@@ -5367,14 +5367,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1475</v>
+        <v>2185</v>
       </c>
       <c r="E215" t="n">
-        <v>-33.59319553508311</v>
+        <v>-9.380826344744387</v>
       </c>
     </row>
     <row r="216">
@@ -5390,14 +5390,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>3059</v>
+        <v>3654</v>
       </c>
       <c r="E216" t="n">
-        <v>-27.28544937257741</v>
+        <v>-16.58088771383107</v>
       </c>
     </row>
     <row r="217">
@@ -5413,14 +5413,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>4889</v>
+        <v>5843</v>
       </c>
       <c r="E217" t="n">
-        <v>-8.402237903251642</v>
+        <v>-5.122568185538579</v>
       </c>
     </row>
     <row r="218">
@@ -5436,14 +5436,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1143</v>
+        <v>1225</v>
       </c>
       <c r="E218" t="n">
-        <v>7.0669471962721</v>
+        <v>-0.5383355501549336</v>
       </c>
     </row>
     <row r="219">
@@ -5459,14 +5459,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2456</v>
+        <v>2645</v>
       </c>
       <c r="E219" t="n">
-        <v>0.8363653611933586</v>
+        <v>-3.545518922898194</v>
       </c>
     </row>
     <row r="220">
@@ -5482,14 +5482,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1655</v>
+        <v>2295</v>
       </c>
       <c r="E220" t="n">
-        <v>-22.00781950131617</v>
+        <v>-0.272961517726078</v>
       </c>
     </row>
     <row r="221">
@@ -5505,14 +5505,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1828</v>
+        <v>3150</v>
       </c>
       <c r="E221" t="n">
-        <v>3.67344737984312</v>
+        <v>20.73262249749279</v>
       </c>
     </row>
     <row r="222">
@@ -5528,14 +5528,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1914</v>
+        <v>2438</v>
       </c>
       <c r="E222" t="n">
-        <v>-14.08485433216612</v>
+        <v>-13.40284433751817</v>
       </c>
     </row>
     <row r="223">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1319</v>
+        <v>2430</v>
       </c>
       <c r="E223" t="n">
-        <v>-10.52625716828974</v>
+        <v>11.21782109841871</v>
       </c>
     </row>
     <row r="224">
@@ -5574,14 +5574,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>3083</v>
+        <v>4605</v>
       </c>
       <c r="E224" t="n">
-        <v>0.7688364690664473</v>
+        <v>26.02798898093994</v>
       </c>
     </row>
     <row r="225">
@@ -5597,14 +5597,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>4263</v>
+        <v>5842</v>
       </c>
       <c r="E225" t="n">
-        <v>-12.80420582981398</v>
+        <v>-0.01567700093206836</v>
       </c>
     </row>
     <row r="226">
@@ -5620,14 +5620,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>893</v>
+        <v>1169</v>
       </c>
       <c r="E226" t="n">
-        <v>-21.84581830043239</v>
+        <v>-4.598344128469711</v>
       </c>
     </row>
     <row r="227">
@@ -5643,14 +5643,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>2319</v>
+        <v>2665</v>
       </c>
       <c r="E227" t="n">
-        <v>-5.569699115309601</v>
+        <v>0.7356617465819504</v>
       </c>
     </row>
     <row r="228">
@@ -5666,14 +5666,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1741</v>
+        <v>2323</v>
       </c>
       <c r="E228" t="n">
-        <v>5.210900346517944</v>
+        <v>1.188365524990687</v>
       </c>
     </row>
     <row r="229">
@@ -5689,14 +5689,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1892</v>
+        <v>1931</v>
       </c>
       <c r="E229" t="n">
-        <v>3.495615301139599</v>
+        <v>-38.71068599969313</v>
       </c>
     </row>
     <row r="230">
@@ -5712,14 +5712,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>2112</v>
+        <v>2439</v>
       </c>
       <c r="E230" t="n">
-        <v>10.37226718986719</v>
+        <v>0.03887453486519643</v>
       </c>
     </row>
     <row r="231">
@@ -5735,14 +5735,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1257</v>
+        <v>1614</v>
       </c>
       <c r="E231" t="n">
-        <v>-4.734884092772395</v>
+        <v>-33.58600968943436</v>
       </c>
     </row>
     <row r="232">
@@ -5758,14 +5758,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>2632</v>
+        <v>3348</v>
       </c>
       <c r="E232" t="n">
-        <v>-14.61802202363367</v>
+        <v>-27.29201022800538</v>
       </c>
     </row>
     <row r="233">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>3791</v>
+        <v>5352</v>
       </c>
       <c r="E233" t="n">
-        <v>-11.08107049116616</v>
+        <v>-8.395857625634861</v>
       </c>
     </row>
     <row r="234">
@@ -5804,14 +5804,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1068</v>
+        <v>1251</v>
       </c>
       <c r="E234" t="n">
-        <v>19.57519952473095</v>
+        <v>7.057161349713614</v>
       </c>
     </row>
     <row r="235">
@@ -5827,14 +5827,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>2049</v>
+        <v>2687</v>
       </c>
       <c r="E235" t="n">
-        <v>-11.63784641659215</v>
+        <v>0.8390843050090746</v>
       </c>
     </row>
     <row r="236">
@@ -5850,14 +5850,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1708</v>
+        <v>1811</v>
       </c>
       <c r="E236" t="n">
-        <v>-1.909332431626598</v>
+        <v>-22.01169585223559</v>
       </c>
     </row>
     <row r="237">
@@ -5873,14 +5873,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>2364</v>
+        <v>2001</v>
       </c>
       <c r="E237" t="n">
-        <v>24.9337345639699</v>
+        <v>3.652716836475811</v>
       </c>
     </row>
     <row r="238">
@@ -5896,14 +5896,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>2515</v>
+        <v>2095</v>
       </c>
       <c r="E238" t="n">
-        <v>19.06178661796964</v>
+        <v>-14.09657696085596</v>
       </c>
     </row>
     <row r="239">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1397</v>
+        <v>1444</v>
       </c>
       <c r="E239" t="n">
-        <v>11.14416803571789</v>
+        <v>-10.49999714812916</v>
       </c>
     </row>
     <row r="240">
@@ -5942,14 +5942,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>2842</v>
+        <v>3375</v>
       </c>
       <c r="E240" t="n">
-        <v>7.965951657646864</v>
+        <v>0.7809973463184239</v>
       </c>
     </row>
     <row r="241">
@@ -5965,14 +5965,566 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
+          <t>01/10/2022</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>4667</v>
+      </c>
+      <c r="E241" t="n">
+        <v>-12.79788776726762</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Agricultura, pecuária, produção florestal, pesca e aquicultura</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>977</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-21.89109649103004</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Indústria geral</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>2538</v>
+      </c>
+      <c r="E243" t="n">
+        <v>-5.555929316519526</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1906</v>
+      </c>
+      <c r="E244" t="n">
+        <v>5.237772668865759</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Comércio, reparação de veículos automotores e motocicletas</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>2071</v>
+      </c>
+      <c r="E245" t="n">
+        <v>3.502659719751322</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>2313</v>
+      </c>
+      <c r="E246" t="n">
+        <v>10.40037242981389</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Alojamento e alimentação</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1376</v>
+      </c>
+      <c r="E247" t="n">
+        <v>-4.719785981970281</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Informação, comunicação e atividades financeiras, imobiliárias, profissionais e administrativas</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>2881</v>
+      </c>
+      <c r="E248" t="n">
+        <v>-14.61992325177319</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Administração pública, defesa, seguridade social, educação, saúde humana e serviços sociais</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>4150</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-11.06876022124314</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Agricultura, pecuária, produção florestal, pesca e aquicultura</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
           <t>01/10/2024</t>
         </is>
       </c>
-      <c r="D241" t="n">
-        <v>4426</v>
-      </c>
-      <c r="E241" t="n">
-        <v>16.75955848491288</v>
+      <c r="D250" t="n">
+        <v>1169</v>
+      </c>
+      <c r="E250" t="n">
+        <v>19.61277059765305</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Indústria geral</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>2243</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-11.63350053413641</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>1871</v>
+      </c>
+      <c r="E252" t="n">
+        <v>-1.873702039331759</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Comércio, reparação de veículos automotores e motocicletas</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>2588</v>
+      </c>
+      <c r="E253" t="n">
+        <v>24.94014888765314</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>2754</v>
+      </c>
+      <c r="E254" t="n">
+        <v>19.05899002825888</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Alojamento e alimentação</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>1529</v>
+      </c>
+      <c r="E255" t="n">
+        <v>11.07535156072812</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Informação, comunicação e atividades financeiras, imobiliárias, profissionais e administrativas</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>3111</v>
+      </c>
+      <c r="E256" t="n">
+        <v>7.984859900545582</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Administração pública, defesa, seguridade social, educação, saúde humana e serviços sociais</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>01/10/2024</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>4845</v>
+      </c>
+      <c r="E257" t="n">
+        <v>16.74587153545573</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Agricultura, pecuária, produção florestal, pesca e aquicultura</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1193</v>
+      </c>
+      <c r="E258" t="n">
+        <v>2.070208294415155</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Indústria geral</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>2922</v>
+      </c>
+      <c r="E259" t="n">
+        <v>30.28786611707574</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>2158</v>
+      </c>
+      <c r="E260" t="n">
+        <v>15.37007410786677</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Comércio, reparação de veículos automotores e motocicletas</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-8.611081505916152</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>2358</v>
+      </c>
+      <c r="E262" t="n">
+        <v>-14.36731341497086</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Alojamento e alimentação</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1819</v>
+      </c>
+      <c r="E263" t="n">
+        <v>19.00436702898198</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Informação, comunicação e atividades financeiras, imobiliárias, profissionais e administrativas</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>4017</v>
+      </c>
+      <c r="E264" t="n">
+        <v>29.11217073669918</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Administração pública, defesa, seguridade social, educação, saúde humana e serviços sociais</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>4541</v>
+      </c>
+      <c r="E265" t="n">
+        <v>-6.277686731059062</v>
       </c>
     </row>
   </sheetData>
